--- a/event_feedback_forms/022_culinary_roles_feedback_survey--event_feedback_forms.xlsx
+++ b/event_feedback_forms/022_culinary_roles_feedback_survey--event_feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>other_role</t>
+          <t>Role Other Text</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>frequency_rating</t>
+          <t>Rating Frequency Other</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Comments 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Comments 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Comments 4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Comments 5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Comments 6</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Comments 7</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Comments 8</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Comments 9</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Comments 10</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'chef'}</t>
+          <t>chef</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Chef'}</t>
+          <t>Chef</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'pastry'}</t>
+          <t>pastry</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Pastry'}</t>
+          <t>Pastry</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'sous'}</t>
+          <t>sous</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Sous'}</t>
+          <t>Sous</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'1-2'}</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '1-2'}</t>
+          <t>1-2</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'3-4'}</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '3-4'}</t>
+          <t>3-4</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'6-7'}</t>
+          <t>6-7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '6-7'}</t>
+          <t>6-7</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'8-10'}</t>
+          <t>8-10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': '8-10'}</t>
+          <t>8-10</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
     </row>
